--- a/data/final/player_stats.xlsx
+++ b/data/final/player_stats.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
   <si>
     <t>pace</t>
   </si>
@@ -35,6 +35,9 @@
     <t>Player</t>
   </si>
   <si>
+    <t>total</t>
+  </si>
+  <si>
     <t>Bruno Fernandes</t>
   </si>
   <si>
@@ -93,12 +96,6 @@
   </si>
   <si>
     <t>Ayden Heaven</t>
-  </si>
-  <si>
-    <t>André Onana</t>
-  </si>
-  <si>
-    <t>Tyler Fredricson</t>
   </si>
   <si>
     <t>Lisandro Martínez</t>
@@ -162,7 +159,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:H22"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -187,6 +184,9 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
@@ -208,7 +208,10 @@
         <v>8.891089951042959</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>64.76018300144858</v>
       </c>
     </row>
     <row r="3">
@@ -231,7 +234,10 @@
         <v>2.8845770478745365</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>52.75183734988584</v>
       </c>
     </row>
     <row r="4">
@@ -254,7 +260,10 @@
         <v>10.933872118280657</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>60.47790468806103</v>
       </c>
     </row>
     <row r="5">
@@ -277,7 +286,10 @@
         <v>13.349078451094705</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="H5" s="2" t="n">
+        <v>63.439428284304256</v>
       </c>
     </row>
     <row r="6">
@@ -300,7 +312,10 @@
         <v>8.99261314049438</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="H6" s="2" t="n">
+        <v>57.12676909472717</v>
       </c>
     </row>
     <row r="7">
@@ -323,7 +338,10 @@
         <v>13.41319111360548</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="H7" s="2" t="n">
+        <v>57.620357887425705</v>
       </c>
     </row>
     <row r="8">
@@ -346,7 +364,10 @@
         <v>6.758794812863831</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="H8" s="2" t="n">
+        <v>55.29713405749219</v>
       </c>
     </row>
     <row r="9">
@@ -369,7 +390,10 @@
         <v>11.747745461646748</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="H9" s="2" t="n">
+        <v>71.09515466231055</v>
       </c>
     </row>
     <row r="10">
@@ -392,7 +416,10 @@
         <v>14.430311212277198</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="H10" s="2" t="n">
+        <v>64.15156233285352</v>
       </c>
     </row>
     <row r="11">
@@ -415,7 +442,10 @@
         <v>20.0</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="H11" s="2" t="n">
+        <v>43.2768008509944</v>
       </c>
     </row>
     <row r="12">
@@ -438,7 +468,10 @@
         <v>10.715220376597017</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="H12" s="2" t="n">
+        <v>45.25145615041509</v>
       </c>
     </row>
     <row r="13">
@@ -461,7 +494,10 @@
         <v>10.501741225031907</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="H13" s="2" t="n">
+        <v>48.107340698599614</v>
       </c>
     </row>
     <row r="14">
@@ -484,7 +520,10 @@
         <v>7.899839777479486</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="H14" s="2" t="n">
+        <v>49.21697529603068</v>
       </c>
     </row>
     <row r="15">
@@ -507,7 +546,10 @@
         <v>19.93893539566173</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="H15" s="2" t="n">
+        <v>62.10361154778879</v>
       </c>
     </row>
     <row r="16">
@@ -530,7 +572,10 @@
         <v>15.097636262980425</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="H16" s="2" t="n">
+        <v>51.26763683855403</v>
       </c>
     </row>
     <row r="17">
@@ -553,7 +598,10 @@
         <v>10.186935885931485</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="H17" s="2" t="n">
+        <v>57.93488323747987</v>
       </c>
     </row>
     <row r="18">
@@ -576,7 +624,10 @@
         <v>9.683277107756867</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="H18" s="2" t="n">
+        <v>54.035808007831974</v>
       </c>
     </row>
     <row r="19">
@@ -599,7 +650,10 @@
         <v>15.072195473837844</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="H19" s="2" t="n">
+        <v>48.09781613201839</v>
       </c>
     </row>
     <row r="20">
@@ -622,7 +676,10 @@
         <v>3.946302451930796</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="H20" s="2" t="n">
+        <v>31.533816108754053</v>
       </c>
     </row>
     <row r="21">
@@ -645,76 +702,36 @@
         <v>11.9677288299768</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="H21" s="2" t="n">
+        <v>29.717690098388385</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>0.0</v>
+        <v>20.0</v>
       </c>
       <c r="B22" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="C22" s="2" t="n">
-        <v>0.0</v>
+        <v>1.4997164997164991</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>0.0</v>
+        <v>20.0</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>0.0</v>
+        <v>3.1152073732718892</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>0.0</v>
+        <v>2.3457867100605614</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="B23" s="2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="C23" s="2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="D23" s="2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="E23" s="2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="F23" s="2" t="n">
-        <v>0.1540035900619034</v>
-      </c>
-      <c r="G23" s="4" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="n">
-        <v>20.0</v>
-      </c>
-      <c r="B24" s="2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="C24" s="2" t="n">
-        <v>1.4997164997164991</v>
-      </c>
-      <c r="D24" s="2" t="n">
-        <v>20.0</v>
-      </c>
-      <c r="E24" s="2" t="n">
-        <v>3.1152073732718892</v>
-      </c>
-      <c r="F24" s="2" t="n">
-        <v>2.3457867100605614</v>
-      </c>
-      <c r="G24" s="4" t="s">
-        <v>29</v>
+      <c r="H22" s="2" t="n">
+        <v>46.96071058304894</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/player_stats.xlsx
+++ b/data/final/player_stats.xlsx
@@ -38,64 +38,64 @@
     <t>total</t>
   </si>
   <si>
+    <t>Matthijs de Ligt</t>
+  </si>
+  <si>
+    <t>Diogo Dalot</t>
+  </si>
+  <si>
+    <t>Harry Maguire</t>
+  </si>
+  <si>
+    <t>Noussair Mazraoui</t>
+  </si>
+  <si>
+    <t>Joshua Zirkzee</t>
+  </si>
+  <si>
+    <t>Ayden Heaven</t>
+  </si>
+  <si>
+    <t>Bryan Mbeumo</t>
+  </si>
+  <si>
+    <t>Luke Shaw</t>
+  </si>
+  <si>
+    <t>Altay Bayındır</t>
+  </si>
+  <si>
+    <t>Leny Yoro</t>
+  </si>
+  <si>
+    <t>Senne Lammens</t>
+  </si>
+  <si>
+    <t>Patrick Dorgu</t>
+  </si>
+  <si>
+    <t>Benjamin Šeško</t>
+  </si>
+  <si>
+    <t>Mason Mount</t>
+  </si>
+  <si>
+    <t>Kobbie Mainoo</t>
+  </si>
+  <si>
     <t>Bruno Fernandes</t>
   </si>
   <si>
-    <t>Bryan Mbeumo</t>
-  </si>
-  <si>
-    <t>Luke Shaw</t>
-  </si>
-  <si>
-    <t>Matthijs de Ligt</t>
-  </si>
-  <si>
     <t>Amad Diallo</t>
   </si>
   <si>
-    <t>Diogo Dalot</t>
-  </si>
-  <si>
     <t>Matheus Cunha</t>
   </si>
   <si>
     <t>Casemiro</t>
   </si>
   <si>
-    <t>Leny Yoro</t>
-  </si>
-  <si>
-    <t>Senne Lammens</t>
-  </si>
-  <si>
-    <t>Patrick Dorgu</t>
-  </si>
-  <si>
-    <t>Benjamin Šeško</t>
-  </si>
-  <si>
-    <t>Mason Mount</t>
-  </si>
-  <si>
-    <t>Altay Bayındır</t>
-  </si>
-  <si>
-    <t>Harry Maguire</t>
-  </si>
-  <si>
-    <t>Noussair Mazraoui</t>
-  </si>
-  <si>
-    <t>Joshua Zirkzee</t>
-  </si>
-  <si>
     <t>Manuel Ugarte</t>
-  </si>
-  <si>
-    <t>Kobbie Mainoo</t>
-  </si>
-  <si>
-    <t>Ayden Heaven</t>
   </si>
   <si>
     <t>Lisandro Martínez</t>
@@ -190,522 +190,522 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>10.329103380695738</v>
+        <v>7.848383500557413</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>8.551417918294277</v>
+        <v>5.181448741411733</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>20.0</v>
+        <v>12.446528011745404</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>8.765034811675669</v>
+        <v>9.69891845146454</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>8.22353693973994</v>
+        <v>14.915071128030455</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>8.891089951042959</v>
+        <v>13.349078451094705</v>
       </c>
       <c r="G2" s="4" t="s">
         <v>8</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>64.76018300144858</v>
+        <v>63.439428284304256</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>8.535564435564435</v>
+        <v>8.473426573426574</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>20.0</v>
+        <v>5.695864009539128</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>6.499426863063227</v>
+        <v>8.554732736550918</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>9.560379602461982</v>
+        <v>8.825380572024594</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>5.271889400921658</v>
+        <v>12.65776288227901</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>2.8845770478745365</v>
+        <v>13.41319111360548</v>
       </c>
       <c r="G3" s="4" t="s">
         <v>9</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>52.75183734988584</v>
+        <v>57.620357887425705</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>11.116251354279525</v>
+        <v>3.1213017751479293</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>1.9654706785045897</v>
+        <v>9.338305243878274</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>18.009364826266232</v>
+        <v>3.7103935565474018</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>3.7721175157537083</v>
+        <v>0.0</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>14.68082819497631</v>
+        <v>20.0</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>10.933872118280657</v>
+        <v>15.097636262980425</v>
       </c>
       <c r="G4" s="4" t="s">
         <v>10</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>60.47790468806103</v>
+        <v>51.26763683855403</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>7.848383500557413</v>
+        <v>13.619466248037677</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>5.181448741411733</v>
+        <v>0.7001676717319149</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>12.446528011745404</v>
+        <v>8.061344061344059</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>9.69891845146454</v>
+        <v>9.116639266042757</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>14.915071128030455</v>
+        <v>16.25033010439199</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>13.349078451094705</v>
+        <v>10.186935885931485</v>
       </c>
       <c r="G5" s="4" t="s">
         <v>11</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>63.439428284304256</v>
+        <v>57.93488323747987</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>13.058126084441872</v>
+        <v>5.796064400715563</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>7.36082154658399</v>
+        <v>13.33197043385536</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>6.7445328497960055</v>
+        <v>1.6153978014443127</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>12.07051539579754</v>
+        <v>9.908427382053654</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>8.90016007761339</v>
+        <v>13.700670882006216</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>8.99261314049438</v>
+        <v>9.683277107756867</v>
       </c>
       <c r="G6" s="4" t="s">
         <v>12</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>57.12676909472717</v>
+        <v>54.035808007831974</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>8.473426573426574</v>
+        <v>2.107023411371238</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>5.695864009539128</v>
+        <v>3.045729372033829</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>8.554732736550918</v>
+        <v>1.678354547919765</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>8.825380572024594</v>
+        <v>0.0</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>12.65776288227901</v>
+        <v>10.918853937086755</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>13.41319111360548</v>
+        <v>11.9677288299768</v>
       </c>
       <c r="G7" s="4" t="s">
         <v>13</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>57.620357887425705</v>
+        <v>29.717690098388385</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>11.085754985754983</v>
+        <v>8.535564435564435</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>12.926294402371353</v>
+        <v>20.0</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>4.212856212856212</v>
+        <v>6.499426863063227</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>13.104258016405666</v>
+        <v>9.560379602461982</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>7.209175627240143</v>
+        <v>5.271889400921658</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>6.758794812863831</v>
+        <v>2.8845770478745365</v>
       </c>
       <c r="G8" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>55.29713405749219</v>
+        <v>52.75183734988584</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>9.95145631067961</v>
+        <v>11.116251354279525</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>12.484902849160562</v>
+        <v>1.9654706785045897</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>10.197202430212137</v>
+        <v>18.009364826266232</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>14.419038429814217</v>
+        <v>3.7721175157537083</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>12.29480918079728</v>
+        <v>14.68082819497631</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>11.747745461646748</v>
+        <v>10.933872118280657</v>
       </c>
       <c r="G9" s="4" t="s">
         <v>15</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>71.09515466231055</v>
+        <v>60.47790468806103</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>13.295546558704457</v>
+        <v>12.602564102564102</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>1.592881453190106</v>
+        <v>0.0</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>10.966188860925698</v>
+        <v>10.484155484155481</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>9.703665535653226</v>
+        <v>18.91820234113712</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>14.162968712102835</v>
+        <v>0.15975422427035327</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>14.430311212277198</v>
+        <v>19.93893539566173</v>
       </c>
       <c r="G10" s="4" t="s">
         <v>16</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>64.15156233285352</v>
+        <v>62.10361154778879</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>4.854700854700855</v>
+        <v>13.295546558704457</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>0.0</v>
+        <v>1.592881453190106</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>18.320922320922318</v>
+        <v>10.966188860925698</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>0.0</v>
+        <v>9.703665535653226</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>0.10117767537122374</v>
+        <v>14.162968712102835</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>20.0</v>
+        <v>14.430311212277198</v>
       </c>
       <c r="G11" s="4" t="s">
         <v>17</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>43.2768008509944</v>
+        <v>64.15156233285352</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>7.594871794871794</v>
+        <v>4.854700854700855</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>2.546332671232271</v>
+        <v>0.0</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>3.8939978939978936</v>
+        <v>18.320922320922318</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>6.197553053830228</v>
+        <v>0.0</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>14.303480359885887</v>
+        <v>0.10117767537122374</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>10.715220376597017</v>
+        <v>20.0</v>
       </c>
       <c r="G12" s="4" t="s">
         <v>18</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>45.25145615041509</v>
+        <v>43.2768008509944</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>2.8986866791744843</v>
+        <v>7.594871794871794</v>
       </c>
       <c r="B13" s="2" t="n">
-        <v>14.957891299688074</v>
+        <v>2.546332671232271</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>1.3709612734002976</v>
+        <v>3.8939978939978936</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>5.158826771827502</v>
+        <v>6.197553053830228</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>13.219233449477352</v>
+        <v>14.303480359885887</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>10.501741225031907</v>
+        <v>10.715220376597017</v>
       </c>
       <c r="G13" s="4" t="s">
         <v>19</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>48.107340698599614</v>
+        <v>45.25145615041509</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>6.483640303358613</v>
+        <v>2.8986866791744843</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>15.130481220101966</v>
+        <v>14.957891299688074</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>4.046403539361284</v>
+        <v>1.3709612734002976</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>7.855024163784114</v>
+        <v>5.158826771827502</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>7.8015862919452195</v>
+        <v>13.219233449477352</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>7.899839777479486</v>
+        <v>10.501741225031907</v>
       </c>
       <c r="G14" s="4" t="s">
         <v>20</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>49.21697529603068</v>
+        <v>48.107340698599614</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>12.602564102564102</v>
+        <v>6.483640303358613</v>
       </c>
       <c r="B15" s="2" t="n">
-        <v>0.0</v>
+        <v>15.130481220101966</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>10.484155484155481</v>
+        <v>4.046403539361284</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>18.91820234113712</v>
+        <v>7.855024163784114</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>0.15975422427035327</v>
+        <v>7.8015862919452195</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>19.93893539566173</v>
+        <v>7.899839777479486</v>
       </c>
       <c r="G15" s="4" t="s">
         <v>21</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>62.10361154778879</v>
+        <v>49.21697529603068</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>3.1213017751479293</v>
+        <v>9.2989010989011</v>
       </c>
       <c r="B16" s="2" t="n">
-        <v>9.338305243878274</v>
+        <v>2.9266203887966764</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>3.7103935565474018</v>
+        <v>1.8526338526338526</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>0.0</v>
+        <v>6.0985880729103235</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>20.0</v>
+        <v>7.410770243581304</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>15.097636262980425</v>
+        <v>3.946302451930796</v>
       </c>
       <c r="G16" s="4" t="s">
         <v>22</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>51.26763683855403</v>
+        <v>31.533816108754053</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>13.619466248037677</v>
+        <v>10.329103380695738</v>
       </c>
       <c r="B17" s="2" t="n">
-        <v>0.7001676717319149</v>
+        <v>8.551417918294277</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>8.061344061344059</v>
+        <v>20.0</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>9.116639266042757</v>
+        <v>8.765034811675669</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>16.25033010439199</v>
+        <v>8.22353693973994</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>10.186935885931485</v>
+        <v>8.891089951042959</v>
       </c>
       <c r="G17" s="4" t="s">
         <v>23</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>57.93488323747987</v>
+        <v>64.76018300144858</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>5.796064400715563</v>
+        <v>13.058126084441872</v>
       </c>
       <c r="B18" s="2" t="n">
-        <v>13.33197043385536</v>
+        <v>7.36082154658399</v>
       </c>
       <c r="C18" s="2" t="n">
-        <v>1.6153978014443127</v>
+        <v>6.7445328497960055</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>9.908427382053654</v>
+        <v>12.07051539579754</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>13.700670882006216</v>
+        <v>8.90016007761339</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>9.683277107756867</v>
+        <v>8.99261314049438</v>
       </c>
       <c r="G18" s="4" t="s">
         <v>24</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>54.035808007831974</v>
+        <v>57.12676909472717</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>6.907692307692308</v>
+        <v>11.085754985754983</v>
       </c>
       <c r="B19" s="2" t="n">
-        <v>2.5906203854080845</v>
+        <v>12.926294402371353</v>
       </c>
       <c r="C19" s="2" t="n">
-        <v>2.8725193725193714</v>
+        <v>4.212856212856212</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>6.6123922791967225</v>
+        <v>13.104258016405666</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>14.042396313364055</v>
+        <v>7.209175627240143</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>15.072195473837844</v>
+        <v>6.758794812863831</v>
       </c>
       <c r="G19" s="4" t="s">
         <v>25</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>48.09781613201839</v>
+        <v>55.29713405749219</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>9.2989010989011</v>
+        <v>9.95145631067961</v>
       </c>
       <c r="B20" s="2" t="n">
-        <v>2.9266203887966764</v>
+        <v>12.484902849160562</v>
       </c>
       <c r="C20" s="2" t="n">
-        <v>1.8526338526338526</v>
+        <v>10.197202430212137</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>6.0985880729103235</v>
+        <v>14.419038429814217</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>7.410770243581304</v>
+        <v>12.29480918079728</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>3.946302451930796</v>
+        <v>11.747745461646748</v>
       </c>
       <c r="G20" s="4" t="s">
         <v>26</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>31.533816108754053</v>
+        <v>71.09515466231055</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>2.107023411371238</v>
+        <v>6.907692307692308</v>
       </c>
       <c r="B21" s="2" t="n">
-        <v>3.045729372033829</v>
+        <v>2.5906203854080845</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>1.678354547919765</v>
+        <v>2.8725193725193714</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>0.0</v>
+        <v>6.6123922791967225</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>10.918853937086755</v>
+        <v>14.042396313364055</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>11.9677288299768</v>
+        <v>15.072195473837844</v>
       </c>
       <c r="G21" s="4" t="s">
         <v>27</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>29.717690098388385</v>
+        <v>48.09781613201839</v>
       </c>
     </row>
     <row r="22">
